--- a/docs/airlift-pump-design.xlsx
+++ b/docs/airlift-pump-design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\Projects\kawruhnology\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sam294\Documents\Projects\kawruhnology\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BAB657-0BC2-4E1D-B5DF-C70EEF89034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D004E55-056A-4224-996A-2E5CEBA377E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="15180" windowHeight="11385" xr2:uid="{AC3BD9D6-CAE3-4C4D-8869-82B1FC86F58B}"/>
+    <workbookView xWindow="-60" yWindow="0" windowWidth="16935" windowHeight="15585" xr2:uid="{AC3BD9D6-CAE3-4C4D-8869-82B1FC86F58B}"/>
   </bookViews>
   <sheets>
     <sheet name="simulation" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,17 @@
     <definedName name="ExternalData_4" localSheetId="0" hidden="1">simulation!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -496,6 +507,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -973,13 +988,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1029,7 +1049,7 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1038,7 +1058,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1091,11 +1111,11 @@
     <tableColumn id="2" xr3:uid="{EBB15678-70BF-4C33-8E44-D334910B68A8}" uniqueName="2" name="Kategori" queryTableFieldId="2" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{15D7CDA9-6B4C-4908-9082-6FCA454AD738}" uniqueName="3" name="Parameter" queryTableFieldId="3" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{F61542EC-D19C-4583-B3D4-B569B92158BB}" uniqueName="4" name="Simbol" queryTableFieldId="4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8293F415-41A4-4933-94C3-11DBC0B4C251}" uniqueName="5" name="Satuan" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{79480AA7-D66E-4537-B862-32417BCF9C0A}" uniqueName="6" name="Nilai Awal" queryTableFieldId="6" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{C5FFBBEB-9270-4B78-A201-80C36DCDE8BC}" uniqueName="7" name="Rumus Umum" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{0CF8BC47-E6B0-4970-B64F-F3CE9B81547E}" uniqueName="8" name="Formula Excel" queryTableFieldId="8" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C9B4CEDC-061D-4310-9E53-41921BD04E59}" uniqueName="9" name="Keterangan" queryTableFieldId="9" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{8293F415-41A4-4933-94C3-11DBC0B4C251}" uniqueName="5" name="Satuan" queryTableFieldId="5" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{79480AA7-D66E-4537-B862-32417BCF9C0A}" uniqueName="6" name="Nilai Awal" queryTableFieldId="6" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{C5FFBBEB-9270-4B78-A201-80C36DCDE8BC}" uniqueName="7" name="Rumus Umum" queryTableFieldId="7" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{0CF8BC47-E6B0-4970-B64F-F3CE9B81547E}" uniqueName="8" name="Formula Excel" queryTableFieldId="8" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C9B4CEDC-061D-4310-9E53-41921BD04E59}" uniqueName="9" name="Keterangan" queryTableFieldId="9" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1406,7 +1426,7 @@
     <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37" bestFit="1" customWidth="1"/>
@@ -1428,7 +1448,7 @@
       <c r="E1" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G1" t="s">
@@ -1445,28 +1465,28 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1474,29 +1494,29 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>F2/3600</f>
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1504,28 +1524,28 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>124</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1533,29 +1553,29 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f>F3/F4</f>
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1563,29 +1583,29 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="3">
         <f>2*SQRT(F5/PI())</f>
         <v>4.2052208700336005E-2</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1593,29 +1613,29 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <f>F6*100</f>
         <v>4.2052208700336005</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1623,28 +1643,28 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>128</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1652,28 +1672,28 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>1000</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1681,28 +1701,28 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="2">
-        <v>981</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>130</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1710,29 +1730,29 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <f>F9*F10*F8</f>
-        <v>1962000</v>
-      </c>
-      <c r="G11" s="1" t="s">
+        <v>19620</v>
+      </c>
+      <c r="G11" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>131</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1740,29 +1760,29 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>F11/100000</f>
-        <v>19.62</v>
-      </c>
-      <c r="G12" s="1" t="s">
+        <v>0.19620000000000001</v>
+      </c>
+      <c r="G12" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>132</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1770,28 +1790,28 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>133</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1799,29 +1819,29 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <f>F12+F13</f>
-        <v>20.62</v>
-      </c>
-      <c r="G14" s="1" t="s">
+        <v>0.29620000000000002</v>
+      </c>
+      <c r="G14" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>134</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1829,29 +1849,29 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
         <f>F14*100000</f>
-        <v>2062000</v>
-      </c>
-      <c r="G15" s="1" t="s">
+        <v>29620.000000000004</v>
+      </c>
+      <c r="G15" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>135</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1859,28 +1879,28 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="2">
-        <v>12</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="F16" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="G16" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>136</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1888,29 +1908,29 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="1">
         <f>F16*F2</f>
-        <v>60</v>
-      </c>
-      <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1918,29 +1938,29 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="1">
         <f>F17/3600</f>
-        <v>1.6666666666666666E-2</v>
-      </c>
-      <c r="G18" s="1" t="s">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="G18" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1948,28 +1968,28 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="2">
-        <v>75</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="F19" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="G19" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>139</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1977,29 +1997,29 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="3">
         <f>F18*F15/F19</f>
-        <v>458.22222222222217</v>
-      </c>
-      <c r="G20" s="1" t="s">
+        <v>65.822222222222237</v>
+      </c>
+      <c r="G20" t="s">
         <v>106</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>140</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2007,28 +2027,28 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="2">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="F21" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="G21" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>141</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2036,29 +2056,29 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <f>F20*F21</f>
-        <v>5956.8888888888887</v>
-      </c>
-      <c r="G22" s="1" t="s">
+        <v>85.568888888888907</v>
+      </c>
+      <c r="G22" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>142</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2066,28 +2086,28 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="F23" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="G23" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>143</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2095,28 +2115,28 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="2">
-        <v>80</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="F24" s="1">
+        <v>200</v>
+      </c>
+      <c r="G24" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2124,29 +2144,29 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <f>F24*PI()*(F23/2)^2</f>
-        <v>62.831853071795862</v>
-      </c>
-      <c r="G25" s="1" t="s">
+        <v>226.1946710584651</v>
+      </c>
+      <c r="G25" t="s">
         <v>90</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>145</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2154,29 +2174,29 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <f>F25/1000000</f>
-        <v>6.2831853071795856E-5</v>
-      </c>
-      <c r="G26" s="1" t="s">
+        <v>2.261946710584651E-4</v>
+      </c>
+      <c r="G26" t="s">
         <v>93</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>146</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2184,29 +2204,29 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <f>F18/F26</f>
-        <v>265.25823848649225</v>
-      </c>
-      <c r="G27" s="1" t="s">
+        <v>7.3682844024025629</v>
+      </c>
+      <c r="G27" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2214,28 +2234,28 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>1</v>
       </c>
-      <c r="F28" s="2">
-        <v>5</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="F28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G28" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>148</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>112</v>
       </c>
     </row>
